--- a/VerveStacks_TUR_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A78969-0D4F-4277-AFF7-1FDF5965396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AFC6C7-9C1E-4754-B5A4-6F3F1E73065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -4006,7 +4006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C04F7F4F-85A4-462A-8C9D-4EFF3E9312A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B84002C3-0078-4596-9B9D-7584A7B00C8F}">
   <dimension ref="B3:I35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -4853,7 +4853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D80760F-F58A-452C-88F3-EBA9B5EFEB55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B59DB2-1B18-463D-9888-76025C2280BD}">
   <dimension ref="B3:I35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
